--- a/144/DQ Templates and Instructions/Topic 2 DQ 2/Topic 2 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 2 DQ 2/Topic 2 DQ 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 2 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{04F808BF-0000-4781-8875-81665D9480C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AC8AFEC-49F7-4F1A-9289-E7DCB187DF2B}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{04F808BF-0000-4781-8875-81665D9480C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8E5A105-58BF-4673-AD55-E26430D30BFA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F5830A4-E866-4CA9-84DB-696DC6FA58AF}"/>
   </bookViews>
@@ -40,6 +40,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={049BA7CA-E6FB-452D-BC56-DF5861A1D7CD}</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{049BA7CA-E6FB-452D-BC56-DF5861A1D7CD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/e97a0467c60b44109cc4590693526cef?sid=1dd969fd-f5e1-494d-a41a-0426a4489e67</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
   <si>
@@ -329,7 +347,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,17 +414,22 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="14"/>
-      <color theme="10"/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <sz val="14"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -965,11 +988,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1127,12 +1150,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
@@ -1243,6 +1260,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,18 +1276,18 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1719,6 +1742,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{60CFA8B9-55F8-4490-8A13-CC930320C5A2}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -2014,6 +2043,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C3" dT="2026-07-16T19:37:24.78" personId="{60CFA8B9-55F8-4490-8A13-CC930320C5A2}" id="{049BA7CA-E6FB-452D-BC56-DF5861A1D7CD}">
+    <text>https://www.loom.com/share/e97a0467c60b44109cc4590693526cef?sid=1dd969fd-f5e1-494d-a41a-0426a4489e67</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1152617653</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/e97a0467c60b44109cc4590693526cef?sid=1dd969fd-f5e1-494d-a41a-0426a4489e67"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF0CB51-28CD-4D4D-9C7F-D2DE0B4D05F1}">
   <dimension ref="B2:I9"/>
@@ -2095,7 +2138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A634F11-7084-4FE9-B4F6-622DD42176E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A634F11-7084-4FE9-B4F6-622DD42176E5}">
   <dimension ref="B1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2128,10 +2171,10 @@
       <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="92"/>
+      <c r="D3" s="126"/>
     </row>
     <row r="4" spans="2:13" ht="14.45" customHeight="1" thickTop="1">
       <c r="B4" s="75" t="s">
@@ -2235,12 +2278,12 @@
       <c r="I11" s="41">
         <v>15</v>
       </c>
-      <c r="J11" s="93" t="s">
+      <c r="J11" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="94"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="92"/>
     </row>
     <row r="12" spans="2:13" ht="14.45" customHeight="1">
       <c r="B12" s="78"/>
@@ -2252,12 +2295,12 @@
       <c r="I12" s="42">
         <v>15</v>
       </c>
-      <c r="J12" s="95" t="s">
+      <c r="J12" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="95"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="96"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="94"/>
     </row>
     <row r="13" spans="2:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="B13" s="81"/>
@@ -2269,12 +2312,12 @@
       <c r="I13" s="43">
         <v>16</v>
       </c>
-      <c r="J13" s="97" t="s">
+      <c r="J13" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="98"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="96"/>
     </row>
     <row r="14" spans="2:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="B14" s="13"/>
@@ -2286,12 +2329,12 @@
       <c r="I14" s="44">
         <v>16</v>
       </c>
-      <c r="J14" s="99" t="s">
+      <c r="J14" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="100"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="98"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="15" t="str">
@@ -2386,7 +2429,7 @@
       <c r="F22" s="48"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="m/zNtggVzyhvFEs+nlh2xGZH8uzhVVK6rvtEl4YOYe9h33BU3rInvusoVezQLPlqBkdPSQsUQscGeC9swst7Dw==" saltValue="PHha20WM8YJhU/tGVCUSyA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Db23IBO0c7QS5fbnbur53wG8n7hBrQ+RpSiAy6dBpmo7M8Ew7ytCMNwhraP26UC/G1/ivzDK2A4oZMppr4HMRA==" saltValue="z6XvkQJE+g0guCNqlIhEPw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="9">
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B19:F19"/>
@@ -2399,7 +2442,7 @@
     <mergeCell ref="J14:M14"/>
   </mergeCells>
   <conditionalFormatting sqref="C17 F17 C21:C22 F21:F22">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(OR(ISBLANK(C17),_xlfn.ISFORMULA(C17)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2409,6 +2452,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>
   <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2452,11 +2496,11 @@
       <c r="B2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="101" t="str">
+      <c r="C2" s="99" t="str">
         <f>'Inflation Rate &amp; Projection'!C2</f>
         <v>Your Name Here</v>
       </c>
-      <c r="D2" s="102"/>
+      <c r="D2" s="100"/>
       <c r="E2" s="51" t="s">
         <v>8</v>
       </c>
@@ -2465,26 +2509,26 @@
     </row>
     <row r="3" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:10" ht="14.45" customHeight="1" thickTop="1">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="105"/>
-      <c r="I4" s="112" t="s">
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="103"/>
+      <c r="I4" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="113"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="108"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="106"/>
       <c r="I5" s="53" t="s">
         <v>12</v>
       </c>
@@ -2493,12 +2537,12 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B6" s="106"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="108"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="106"/>
       <c r="I6" s="53" t="s">
         <v>14</v>
       </c>
@@ -2507,12 +2551,12 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B7" s="106"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="108"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="106"/>
       <c r="I7" s="53" t="s">
         <v>16</v>
       </c>
@@ -2521,12 +2565,12 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B8" s="106"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="108"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
       <c r="I8" s="53" t="s">
         <v>18</v>
       </c>
@@ -2535,12 +2579,12 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B9" s="106"/>
-      <c r="C9" s="107"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="108"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106"/>
       <c r="I9" s="55" t="s">
         <v>20</v>
       </c>
@@ -2549,36 +2593,36 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="14.45" customHeight="1" thickTop="1">
-      <c r="B10" s="106"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="108"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
     </row>
     <row r="11" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B11" s="106"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="108"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="106"/>
     </row>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="106"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="108"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="106"/>
     </row>
     <row r="13" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B13" s="109"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="111"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="109"/>
     </row>
     <row r="14" spans="2:10" ht="14.45" customHeight="1" thickBot="1">
       <c r="B14" s="57"/>
@@ -2650,19 +2694,19 @@
     </row>
     <row r="18" spans="2:7" ht="27" thickBot="1">
       <c r="B18" s="65"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
     </row>
     <row r="19" spans="2:7" ht="72" customHeight="1" thickBot="1">
-      <c r="B19" s="115" t="str">
+      <c r="B19" s="113" t="str">
         <f>IF($C$2="Your Name Here","Enter Your Name in C2","Part 2: Based on the Inflation Rates, if you made $"&amp;Random!H22&amp;"/hour in "&amp;Random!H23&amp;" "&amp;Random!H26&amp;", how much should you make in "&amp;Random!H23&amp;" "&amp;Random!H28&amp;" to keep up with inflation? How much money would that be a week if you worked 40 hours a week?"&amp;"
 Format all cells as Currency with 2 decimal places.")</f>
         <v>Enter Your Name in C2</v>
       </c>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="117"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
     </row>
     <row r="20" spans="2:7" ht="27.95" customHeight="1" thickBot="1">
       <c r="B20" s="66" t="s">
@@ -4903,96 +4947,96 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:9">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="116" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="120"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="118"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="123"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="121"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="123"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="121"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="121"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="123"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="121"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="121"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="123"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="121"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="121"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="123"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="121"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="121"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="123"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="121"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="121"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="123"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="121"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B10" s="124"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="126"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5012,16 +5056,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5238,6 +5272,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454AD3E4-F790-402D-B12B-9C20629F0D77}">
   <ds:schemaRefs>
@@ -5247,16 +5291,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40BAD010-3473-43F1-A94E-36D2C645882C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECBA3FAA-2FAC-4519-A31B-04A52D17B51F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5273,4 +5307,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40BAD010-3473-43F1-A94E-36D2C645882C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>